--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.21559321774883</v>
+        <v>5.560033897884185</v>
       </c>
       <c r="D2" t="n">
-        <v>24.60406206575285</v>
+        <v>3.998160085684838</v>
       </c>
       <c r="E2" t="n">
-        <v>8.079210593145003</v>
+        <v>1.312871721386063</v>
       </c>
       <c r="F2" t="n">
-        <v>7.424466936010155</v>
+        <v>1.20647587710165</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.83951554708383</v>
+        <v>4.036421276401123</v>
       </c>
       <c r="D3" t="n">
-        <v>18.44590046770766</v>
+        <v>2.997458826002494</v>
       </c>
       <c r="E3" t="n">
-        <v>8.079210593145003</v>
+        <v>1.312871721386063</v>
       </c>
       <c r="F3" t="n">
-        <v>7.424466936010155</v>
+        <v>1.20647587710165</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.52011909478738</v>
+        <v>2.522019352902948</v>
       </c>
       <c r="D4" t="n">
-        <v>11.92439533147876</v>
+        <v>1.937714241365299</v>
       </c>
       <c r="E4" t="n">
-        <v>8.079210593145003</v>
+        <v>1.312871721386063</v>
       </c>
       <c r="F4" t="n">
-        <v>7.424466936010155</v>
+        <v>1.20647587710165</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.31251404708759</v>
+        <v>4.438283532651733</v>
       </c>
       <c r="D5" t="n">
-        <v>16.95095273480763</v>
+        <v>2.75452981940624</v>
       </c>
       <c r="E5" t="n">
-        <v>8.079210593145003</v>
+        <v>1.312871721386063</v>
       </c>
       <c r="F5" t="n">
-        <v>7.424466936010155</v>
+        <v>1.20647587710165</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.63334364640646</v>
+        <v>3.190418342541049</v>
       </c>
       <c r="D6" t="n">
-        <v>19.53917827979916</v>
+        <v>3.175116470467363</v>
       </c>
       <c r="E6" t="n">
-        <v>8.079210593145003</v>
+        <v>1.312871721386063</v>
       </c>
       <c r="F6" t="n">
-        <v>7.424466936010155</v>
+        <v>1.20647587710165</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.89692873463367</v>
+        <v>2.908250919377972</v>
       </c>
       <c r="D7" t="n">
-        <v>14.58855217651604</v>
+        <v>2.370639728683857</v>
       </c>
       <c r="E7" t="n">
-        <v>8.079210593145003</v>
+        <v>1.312871721386063</v>
       </c>
       <c r="F7" t="n">
-        <v>7.424466936010155</v>
+        <v>1.20647587710165</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.0615847130618</v>
+        <v>3.260007515872543</v>
       </c>
       <c r="D8" t="n">
-        <v>16.44943649165882</v>
+        <v>2.673033429894558</v>
       </c>
       <c r="E8" t="n">
-        <v>8.079210593145003</v>
+        <v>1.312871721386063</v>
       </c>
       <c r="F8" t="n">
-        <v>7.424466936010155</v>
+        <v>1.20647587710165</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>42.2039073503996</v>
+        <v>6.858134944439936</v>
       </c>
       <c r="D9" t="n">
-        <v>33.49020607224241</v>
+        <v>5.442158486739392</v>
       </c>
       <c r="E9" t="n">
-        <v>8.079210593145003</v>
+        <v>1.312871721386063</v>
       </c>
       <c r="F9" t="n">
-        <v>7.424466936010155</v>
+        <v>1.20647587710165</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>29.49888483889256</v>
+        <v>4.793568786320042</v>
       </c>
       <c r="D10" t="n">
-        <v>29.10120293577991</v>
+        <v>4.728945477064235</v>
       </c>
       <c r="E10" t="n">
-        <v>8.079210593145003</v>
+        <v>1.312871721386063</v>
       </c>
       <c r="F10" t="n">
-        <v>7.424466936010155</v>
+        <v>1.20647587710165</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>28.72477802804839</v>
+        <v>4.667776429557864</v>
       </c>
       <c r="D11" t="n">
-        <v>30.54530595252717</v>
+        <v>4.963612217285665</v>
       </c>
       <c r="E11" t="n">
-        <v>8.079210593145003</v>
+        <v>1.312871721386063</v>
       </c>
       <c r="F11" t="n">
-        <v>7.424466936010155</v>
+        <v>1.20647587710165</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>37.69321078486664</v>
+        <v>6.12514675254083</v>
       </c>
       <c r="D12" t="n">
-        <v>7.108863993174241</v>
+        <v>1.155190398890814</v>
       </c>
       <c r="E12" t="n">
-        <v>8.079210593145003</v>
+        <v>1.312871721386063</v>
       </c>
       <c r="F12" t="n">
-        <v>7.424466936010155</v>
+        <v>1.20647587710165</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>15.6177904262672</v>
+        <v>2.537890944268419</v>
       </c>
       <c r="D13" t="n">
-        <v>21.13706216143505</v>
+        <v>3.434772601233196</v>
       </c>
       <c r="E13" t="n">
-        <v>8.079210593145003</v>
+        <v>1.312871721386063</v>
       </c>
       <c r="F13" t="n">
-        <v>7.424466936010155</v>
+        <v>1.20647587710165</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>26.38504713252842</v>
+        <v>4.287570159035868</v>
       </c>
       <c r="D14" t="n">
-        <v>26.40443577075732</v>
+        <v>4.290720812748065</v>
       </c>
       <c r="E14" t="n">
-        <v>8.079210593145003</v>
+        <v>1.312871721386063</v>
       </c>
       <c r="F14" t="n">
-        <v>7.424466936010155</v>
+        <v>1.20647587710165</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
